--- a/pangolin_private_resources_template.xlsx
+++ b/pangolin_private_resources_template.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyData\Τζιρτζιλάκης\ΜΨΔ\Pangolin\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F6EE67-AFC7-45CB-BCD9-F69138E2A939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="2370" yWindow="2745" windowWidth="38700" windowHeight="15285" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Οδηγίες" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Requests" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Οδηγίες" sheetId="1" r:id="rId1"/>
+    <sheet name="Requests" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,135 +26,82 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
-  <si>
-    <t xml:space="preserve">Αίτημα Δημιουργίας Ιδιωτικού Πόρου Pangolin — Οδηγίες</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Συμπληρώστε μία γραμμή ανά ιδιωτικό πόρο στο φύλλο "Requests" και επιστρέψτε το αρχείο.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Μην αλλάζετε τις επικεφαλίδες των στηλών και μην προσθέτετε νέες στήλες.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Συμπληρώνεται αργότερα από τη Μονάδα Ψηφιακής Διακυβέρνησης</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: Destination (IP or CIDR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Υποχρεωτικό. Είτε μία μεμονωμένη IP διεύθυνση host (π.χ. 10.23.25.11) είτε ένα εύρος CIDR για ολόκληρο υποδίκτυο (π.χ. 10.23.25.0/24). Μία μεμονωμένη IP αντιμετωπίζεται ως πόρος τύπου "host", ενώ ένα CIDR αντιμετωπίζεται ως πόρος τύπου "δικτύου" (network/subnet).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: Alias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Προαιρετικό. Εναλλακτικό/φιλικό όνομα (hostname) για τον πόρο, π.χ. rdp-server-a.internal. Χρησιμοποιείται μόνο αν θέλετε να προσπελαύνετε τον πόρο μέσω ονόματος αντί IP.  Δεν ισχύει στην περίπτωση εύρους CIDR. Αν δεν χρειάζεστε κάτι τέτοιο, αφήστε το κενό.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλες: TCP Ports / UDP Ports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ελεύθερο πεδίο κειμένου — γράψτε ό,τι από τα παρακάτω ταιριάζει:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  •  all      — επιτρέπονται όλες οι θύρες αυτού του πρωτοκόλλου</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  •  blocked  — το πρωτόκολλο αυτό μπλοκάρεται εντελώς</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  •  συγκεκριμένο εύρος — θύρες/εύρη χωρισμένα με κόμμα, π.χ. 3389  ή  80,443  ή  8000-9000,443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Μπορείτε να αφήσετε και τα δύο πεδία κενά αν δεν χρειάζεται πρόσβαση σε αυτό το πρωτόκολλο — θα αντιμετωπιστεί ως blocked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: ICMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enabled = επιτρέπεται ping/traceroute προς τον προορισμό. Disabled = το ICMP μπλοκάρεται.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: User Emails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Λίστα email (χωρισμένα με κόμμα) των χρηστών που θα έχουν πρόσβαση σε αυτόν τον πόρο, π.χ. eskouras@uop.gr, kalidiris@uop.gr. Πρόσβαση θα έχουν ΜΟΝΟ αυτοί οι χρήστες — όχι πρόσβαση βάσει ρόλου (role).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Στήλη: Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Προαιρετικό. Οποιαδήποτε άλλη σχετική πληροφορία για το αίτημα.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Παραδείγματα</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCP Ports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDP Ports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Emails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23.25.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user1@uop.gr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23.30.0/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">445,139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disabled</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+  <si>
+    <t>Αίτημα Δημιουργίας Ιδιωτικού Πόρου Pangolin — Οδηγίες</t>
+  </si>
+  <si>
+    <t>Συμπληρώστε μία γραμμή ανά ιδιωτικό πόρο στο φύλλο "Requests" και επιστρέψτε το αρχείο.</t>
+  </si>
+  <si>
+    <t>Μην αλλάζετε τις επικεφαλίδες των στηλών και μην προσθέτετε νέες στήλες.</t>
+  </si>
+  <si>
+    <t>Στήλη: Name</t>
+  </si>
+  <si>
+    <t>Συμπληρώνεται αργότερα από τη Μονάδα Ψηφιακής Διακυβέρνησης</t>
+  </si>
+  <si>
+    <t>Στήλη: Destination (IP or CIDR)</t>
+  </si>
+  <si>
+    <t>Υποχρεωτικό. Είτε μία μεμονωμένη IP διεύθυνση host (π.χ. 10.23.25.11) είτε ένα εύρος CIDR για ολόκληρο υποδίκτυο (π.χ. 10.23.25.0/24). Μία μεμονωμένη IP αντιμετωπίζεται ως πόρος τύπου "host", ενώ ένα CIDR αντιμετωπίζεται ως πόρος τύπου "δικτύου" (network/subnet).</t>
+  </si>
+  <si>
+    <t>Στήλη: Alias</t>
+  </si>
+  <si>
+    <t>Προαιρετικό. Εναλλακτικό/φιλικό όνομα (hostname) για τον πόρο, π.χ. rdp-server-a.internal. Χρησιμοποιείται μόνο αν θέλετε να προσπελαύνετε τον πόρο μέσω ονόματος αντί IP.  Δεν ισχύει στην περίπτωση εύρους CIDR. Αν δεν χρειάζεστε κάτι τέτοιο, αφήστε το κενό.</t>
+  </si>
+  <si>
+    <t>Στήλη: User Emails</t>
+  </si>
+  <si>
+    <t>Στήλη: Notes</t>
+  </si>
+  <si>
+    <t>Προαιρετικό. Οποιαδήποτε άλλη σχετική πληροφορία για το αίτημα.</t>
+  </si>
+  <si>
+    <t>Παραδείγματα</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>User Emails</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>10.23.25.11</t>
+  </si>
+  <si>
+    <t>user1@uop.gr</t>
+  </si>
+  <si>
+    <t>10.23.30.0/24</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
       </rPr>
-      <t xml:space="preserve">user1</t>
+      <t>user1</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">@uop.gr, </t>
@@ -158,66 +110,68 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
       </rPr>
-      <t xml:space="preserve">user2</t>
+      <t>user2</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">@uop.gr</t>
+      <t>@uop.gr</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Ολόκληρο υποδίκτυο</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23.25.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">app14.internal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all</t>
+    <t>Ολόκληρο υποδίκτυο</t>
+  </si>
+  <si>
+    <t>10.23.25.14</t>
+  </si>
+  <si>
+    <t>app14.internal</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
       </rPr>
-      <t xml:space="preserve">user1</t>
+      <t>user1</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">@uop.gr</t>
+      <t>@uop.gr</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Destination (IP or CIDR)</t>
+    <t>Destination (IP or CIDR)</t>
+  </si>
+  <si>
+    <t>Λίστα email (χωρισμένα με κόμμα) των χρηστών που θα έχουν πρόσβαση σε αυτόν τον πόρο, π.χ. user1@uop.gr, user2@uop.gr. Πρόσβαση θα έχουν ΜΟΝΟ αυτοί οι χρήστες — όχι πρόσβαση βάσει ρόλου (role).</t>
+  </si>
+  <si>
+    <t>Operation System</t>
+  </si>
+  <si>
+    <t>Name (Συμπληρώνεται από τη ΜΨΔ)</t>
+  </si>
+  <si>
+    <t>Στήλη: Operation System</t>
+  </si>
+  <si>
+    <t>Συμπληρώνετε Linux ή Windows</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,52 +182,36 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -298,14 +236,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -321,73 +259,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -446,47 +337,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -494,12 +401,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -528,7 +435,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -549,7 +456,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -600,7 +507,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -618,893 +525,689 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="22"/>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
+    <col min="2" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="B25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="F25" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="F27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="5"/>
+      <c r="F28" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H61"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="false" error="Παρακαλώ επιλέξτε Enabled ή Disabled." errorStyle="stop" errorTitle="Μη έγκυρη τιμή" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F61" type="list">
-      <formula1>"Enabled,Disabled"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/pangolin_private_resources_template.xlsx
+++ b/pangolin_private_resources_template.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyData\Τζιρτζιλάκης\ΜΨΔ\Pangolin\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F6EE67-AFC7-45CB-BCD9-F69138E2A939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="2745" windowWidth="38700" windowHeight="15285" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Οδηγίες" sheetId="1" r:id="rId1"/>
-    <sheet name="Requests" sheetId="2" r:id="rId2"/>
+    <sheet name="Οδηγίες" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Requests" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,152 +21,106 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>Αίτημα Δημιουργίας Ιδιωτικού Πόρου Pangolin — Οδηγίες</t>
-  </si>
-  <si>
-    <t>Συμπληρώστε μία γραμμή ανά ιδιωτικό πόρο στο φύλλο "Requests" και επιστρέψτε το αρχείο.</t>
-  </si>
-  <si>
-    <t>Μην αλλάζετε τις επικεφαλίδες των στηλών και μην προσθέτετε νέες στήλες.</t>
-  </si>
-  <si>
-    <t>Στήλη: Name</t>
-  </si>
-  <si>
-    <t>Συμπληρώνεται αργότερα από τη Μονάδα Ψηφιακής Διακυβέρνησης</t>
-  </si>
-  <si>
-    <t>Στήλη: Destination (IP or CIDR)</t>
-  </si>
-  <si>
-    <t>Υποχρεωτικό. Είτε μία μεμονωμένη IP διεύθυνση host (π.χ. 10.23.25.11) είτε ένα εύρος CIDR για ολόκληρο υποδίκτυο (π.χ. 10.23.25.0/24). Μία μεμονωμένη IP αντιμετωπίζεται ως πόρος τύπου "host", ενώ ένα CIDR αντιμετωπίζεται ως πόρος τύπου "δικτύου" (network/subnet).</t>
-  </si>
-  <si>
-    <t>Στήλη: Alias</t>
-  </si>
-  <si>
-    <t>Προαιρετικό. Εναλλακτικό/φιλικό όνομα (hostname) για τον πόρο, π.χ. rdp-server-a.internal. Χρησιμοποιείται μόνο αν θέλετε να προσπελαύνετε τον πόρο μέσω ονόματος αντί IP.  Δεν ισχύει στην περίπτωση εύρους CIDR. Αν δεν χρειάζεστε κάτι τέτοιο, αφήστε το κενό.</t>
-  </si>
-  <si>
-    <t>Στήλη: User Emails</t>
-  </si>
-  <si>
-    <t>Στήλη: Notes</t>
-  </si>
-  <si>
-    <t>Προαιρετικό. Οποιαδήποτε άλλη σχετική πληροφορία για το αίτημα.</t>
-  </si>
-  <si>
-    <t>Παραδείγματα</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>Alias</t>
-  </si>
-  <si>
-    <t>User Emails</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>10.23.25.11</t>
-  </si>
-  <si>
-    <t>user1@uop.gr</t>
-  </si>
-  <si>
-    <t>10.23.30.0/24</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>user1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">@uop.gr, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>user2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>@uop.gr</t>
-    </r>
-  </si>
-  <si>
-    <t>Ολόκληρο υποδίκτυο</t>
-  </si>
-  <si>
-    <t>10.23.25.14</t>
-  </si>
-  <si>
-    <t>app14.internal</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>user1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>@uop.gr</t>
-    </r>
-  </si>
-  <si>
-    <t>Destination (IP or CIDR)</t>
-  </si>
-  <si>
-    <t>Λίστα email (χωρισμένα με κόμμα) των χρηστών που θα έχουν πρόσβαση σε αυτόν τον πόρο, π.χ. user1@uop.gr, user2@uop.gr. Πρόσβαση θα έχουν ΜΟΝΟ αυτοί οι χρήστες — όχι πρόσβαση βάσει ρόλου (role).</t>
-  </si>
-  <si>
-    <t>Operation System</t>
-  </si>
-  <si>
-    <t>Name (Συμπληρώνεται από τη ΜΨΔ)</t>
-  </si>
-  <si>
-    <t>Στήλη: Operation System</t>
-  </si>
-  <si>
-    <t>Συμπληρώνετε Linux ή Windows</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">Αίτημα Δημιουργίας Ιδιωτικού Πόρου Pangolin — Οδηγίες</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Συμπληρώστε μία γραμμή ανά ιδιωτικό πόρο στο φύλλο "Requests" και επιστρέψτε το αρχείο.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μην αλλάζετε τις επικεφαλίδες των στηλών και μην προσθέτετε νέες στήλες.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Συμπληρώνεται αργότερα από τη Μονάδα Ψηφιακής Διακυβέρνησης με την πόλη/τοποθεσία του πόρου (π.χ. "Πάτρα") — δεν συμπληρώνεται από τον αιτούντα. Χρησιμοποιείται ως το πρώτο τμήμα του τελικού ονόματος του πόρου (βλ. στήλη User Emails).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: Operation System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Συμπληρώνετε Linux ή Windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: Destination (IP or CIDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Υποχρεωτικό. Είτε μία μεμονωμένη IP διεύθυνση host (π.χ. 10.23.25.11) είτε ένα εύρος CIDR για ολόκληρο υποδίκτυο (π.χ. 10.23.25.0/24). Μία μεμονωμένη IP αντιμετωπίζεται ως πόρος τύπου "host", ενώ ένα CIDR αντιμετωπίζεται ως πόρος τύπου "δικτύου" (network/subnet).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: Alias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Προαιρετικό. Εναλλακτικό/φιλικό όνομα (hostname) για τον πόρο, π.χ. rdp-server-a.internal. Χρησιμοποιείται μόνο αν θέλετε να προσπελαύνετε τον πόρο μέσω ονόματος αντί IP.  Δεν ισχύει στην περίπτωση εύρους CIDR. Αν δεν χρειάζεστε κάτι τέτοιο, αφήστε το κενό.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: User Emails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λίστα email (χωρισμένα με κόμμα) των χρηστών που θα έχουν πρόσβαση σε αυτόν τον πόρο, π.χ. user1@uop.gr, user2@uop.gr. Κάθε email δημιουργεί τον ΔΙΚΟ ΤΟΥ ξεχωριστό πόρο (π.χ. 2 email = 2 πόροι), ώστε η πρόσβαση να δίνεται ξεχωριστά ανά χρήστη — όχι πρόσβαση βάσει ρόλου (role). Το όνομα κάθε πόρου παράγεται αυτόματα ως "&lt;πόλη&gt;-&lt;username&gt;-&lt;vlan&gt;-&lt;z&gt;" (π.χ. ktsouvalis@uop.gr στο 10.23.2.50, πόλη "Πάτρα" -&gt; patra-ktsouvalis-2302-50).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Στήλη: Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Προαιρετικό. Οποιαδήποτε άλλη σχετική πληροφορία για το αίτημα.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Παραδείγματα</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Emails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23.25.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user1@uop.gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23.30.0/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user1@uop.gr, user2@uop.gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ολόκληρο υποδίκτυο</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23.25.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name (Συμπληρώνεται από τη ΜΨΔ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination (IP or CIDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alias</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,36 +131,52 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -236,14 +201,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -259,26 +224,73 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -337,63 +349,47 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -401,12 +397,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -435,7 +431,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -456,7 +452,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -507,7 +503,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -525,208 +521,209 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" customWidth="1"/>
-    <col min="2" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="6" max="8" width="22" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="4" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="4" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
+      <c r="D25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="5" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="2" t="s">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="3"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -734,7 +731,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -742,7 +739,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -750,7 +747,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -758,7 +755,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -766,7 +763,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -774,7 +771,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -782,7 +779,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -790,7 +787,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -798,7 +795,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -806,7 +803,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -814,7 +811,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -822,7 +819,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -830,7 +827,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -838,7 +835,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -846,7 +843,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -854,7 +851,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -862,7 +859,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -870,7 +867,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -878,7 +875,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -886,7 +883,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -894,7 +891,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -902,7 +899,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -910,7 +907,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -918,7 +915,7 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -926,7 +923,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -934,7 +931,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -942,7 +939,7 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -950,7 +947,7 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -958,7 +955,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -966,7 +963,7 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -974,7 +971,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -982,7 +979,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -990,7 +987,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -998,7 +995,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -1006,7 +1003,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -1014,7 +1011,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1022,7 +1019,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -1030,7 +1027,7 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -1038,7 +1035,7 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -1046,7 +1043,7 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1054,7 +1051,7 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -1062,7 +1059,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1070,7 +1067,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -1078,7 +1075,7 @@
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -1086,7 +1083,7 @@
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -1094,7 +1091,7 @@
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1102,7 +1099,7 @@
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -1110,7 +1107,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1118,7 +1115,7 @@
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -1126,7 +1123,7 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -1134,7 +1131,7 @@
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -1142,7 +1139,7 @@
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -1150,7 +1147,7 @@
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -1158,7 +1155,7 @@
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -1166,7 +1163,7 @@
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -1174,7 +1171,7 @@
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -1182,7 +1179,7 @@
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -1190,7 +1187,7 @@
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -1198,7 +1195,7 @@
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -1207,7 +1204,12 @@
       <c r="F61" s="7"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/pangolin_private_resources_template.xlsx
+++ b/pangolin_private_resources_template.xlsx
@@ -74,13 +74,13 @@
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Operation System</t>
-  </si>
-  <si>
     <t xml:space="preserve">Destination</t>
   </si>
   <si>
     <t xml:space="preserve">Ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alias</t>
   </si>
   <si>
     <t xml:space="preserve">User Emails</t>
@@ -553,14 +553,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -667,13 +667,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
         <v>24</v>
       </c>
@@ -681,13 +681,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
         <v>26</v>
       </c>
@@ -697,21 +697,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
